--- a/locators.xlsx
+++ b/locators.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="268">
   <si>
     <t>page</t>
   </si>
@@ -824,6 +824,9 @@
   </si>
   <si>
     <t>BettingRulesNG</t>
+  </si>
+  <si>
+    <t>howtobet2</t>
   </si>
 </sst>
 </file>
@@ -831,7 +834,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -869,6 +872,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -938,7 +947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -962,10 +971,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -979,43 +988,55 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1323,12 +1344,12 @@
   <dimension ref="A1:F112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="25.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="18.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="34.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="36.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="15" width="25.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="18.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="34.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="36.71928571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="8" width="37.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1347,11 +1368,11 @@
       <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="11" t="s">
         <v>229</v>
       </c>
@@ -1364,7 +1385,7 @@
       <c r="D2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="29" t="s">
         <v>231</v>
       </c>
       <c r="F2" s="13">
@@ -1384,10 +1405,10 @@
       <c r="D3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="F3" s="14"/>
+      <c r="F3" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="11" t="s">
@@ -1402,10 +1423,10 @@
       <c r="D4" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="14"/>
+      <c r="E4" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="11" t="s">
@@ -1420,10 +1441,10 @@
       <c r="D5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="F5" s="14"/>
+      <c r="F5" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="11" t="s">
@@ -1438,10 +1459,10 @@
       <c r="D6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="F6" s="14"/>
+      <c r="F6" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="11" t="s">
@@ -1456,10 +1477,10 @@
       <c r="D7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="F7" s="14"/>
+      <c r="F7" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="11" t="s">
@@ -1474,10 +1495,10 @@
       <c r="D8" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="14"/>
+      <c r="E8" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="11" t="s">
@@ -1492,10 +1513,10 @@
       <c r="D9" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="14"/>
+      <c r="E9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="11" t="s">
@@ -1510,10 +1531,10 @@
       <c r="D10" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="14"/>
+      <c r="E10" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="11" t="s">
@@ -1528,10 +1549,10 @@
       <c r="D11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="F11" s="14"/>
+      <c r="F11" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="11" t="s">
@@ -1546,10 +1567,10 @@
       <c r="D12" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="14"/>
+      <c r="E12" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="11" t="s">
@@ -1564,10 +1585,10 @@
       <c r="D13" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="14"/>
+      <c r="E13" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="11" t="s">
@@ -1582,10 +1603,10 @@
       <c r="D14" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="14"/>
+      <c r="E14" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="11" t="s">
@@ -1600,10 +1621,10 @@
       <c r="D15" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="14"/>
+      <c r="E15" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="11" t="s">
@@ -1618,10 +1639,10 @@
       <c r="D16" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="14"/>
+      <c r="E16" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="11" t="s">
@@ -1636,10 +1657,10 @@
       <c r="D17" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="14"/>
+      <c r="E17" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="11" t="s">
@@ -1654,10 +1675,10 @@
       <c r="D18" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="14"/>
+      <c r="E18" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="11" t="s">
@@ -1669,13 +1690,13 @@
       <c r="C19" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="14"/>
+      <c r="E19" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="11" t="s">
@@ -1690,10 +1711,10 @@
       <c r="D20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="27">
         <v>1</v>
       </c>
     </row>
@@ -1710,236 +1731,246 @@
       <c r="D21" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="27">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="14"/>
+      <c r="A22" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="14"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="14"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="14"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="14"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="14"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="14"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="14"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="14"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="14"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="14"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="14"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="14"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="14"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="14"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="14"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="14"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="14"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="14"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="14"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="14"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="11"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="14"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="14"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="14"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="14"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="14"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="14"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="14"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="5"/>
@@ -2066,8 +2097,8 @@
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="14"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="5"/>
@@ -2226,192 +2257,192 @@
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="14"/>
+      <c r="E85" s="29"/>
+      <c r="F85" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="5"/>
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="14"/>
+      <c r="E86" s="29"/>
+      <c r="F86" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="5"/>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="14"/>
+      <c r="E87" s="29"/>
+      <c r="F87" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="5"/>
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="14"/>
+      <c r="E88" s="29"/>
+      <c r="F88" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="5"/>
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="14"/>
+      <c r="E89" s="29"/>
+      <c r="F89" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="5"/>
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="14"/>
+      <c r="E90" s="29"/>
+      <c r="F90" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="5"/>
       <c r="B91" s="11"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="14"/>
+      <c r="E91" s="29"/>
+      <c r="F91" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="5"/>
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="14"/>
+      <c r="E92" s="29"/>
+      <c r="F92" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="5"/>
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="14"/>
+      <c r="E93" s="29"/>
+      <c r="F93" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="5"/>
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="14"/>
+      <c r="E94" s="29"/>
+      <c r="F94" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="5"/>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="14"/>
+      <c r="E95" s="29"/>
+      <c r="F95" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="5"/>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="14"/>
+      <c r="E96" s="29"/>
+      <c r="F96" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="5"/>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="14"/>
+      <c r="E97" s="29"/>
+      <c r="F97" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="5"/>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="14"/>
+      <c r="E98" s="29"/>
+      <c r="F98" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="5"/>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="14"/>
+      <c r="E99" s="29"/>
+      <c r="F99" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="5"/>
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="14"/>
+      <c r="E100" s="29"/>
+      <c r="F100" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="5"/>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="14"/>
+      <c r="E101" s="29"/>
+      <c r="F101" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="5"/>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="14"/>
+      <c r="E102" s="29"/>
+      <c r="F102" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="5"/>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="14"/>
+      <c r="E103" s="29"/>
+      <c r="F103" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="5"/>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="14"/>
+      <c r="E104" s="29"/>
+      <c r="F104" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="5"/>
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="14"/>
+      <c r="E105" s="29"/>
+      <c r="F105" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="5"/>
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="14"/>
+      <c r="E106" s="29"/>
+      <c r="F106" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="5"/>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="14"/>
+      <c r="E107" s="29"/>
+      <c r="F107" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="5"/>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
       <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="14"/>
+      <c r="E108" s="29"/>
+      <c r="F108" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="11"/>
@@ -2443,7 +2474,7 @@
       <c r="C112" s="11"/>
       <c r="D112" s="11"/>
       <c r="E112" s="5"/>
-      <c r="F112" s="14"/>
+      <c r="F112" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3179,12 +3210,12 @@
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="17.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="31.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="29.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="15" width="22.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="17.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="31.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="29.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -3203,7 +3234,7 @@
       <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3724,7 +3755,7 @@
     <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -3808,11 +3839,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="17.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="15" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="17.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="17.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="18.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="21.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="16" width="21.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -3922,7 +3953,7 @@
       <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="11" t="s">
@@ -3937,7 +3968,7 @@
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="11" t="s">
@@ -3946,13 +3977,13 @@
       <c r="B9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="28" t="s">
         <v>210</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="11" t="s">
@@ -3967,7 +3998,7 @@
       <c r="D10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="11" t="s">
@@ -3982,7 +4013,7 @@
       <c r="D11" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3997,11 +4028,11 @@
   <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="21.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="16.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="20.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="37.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="15" width="21.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="16.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="20.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="37.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -4017,7 +4048,7 @@
       <c r="D1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="26" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4696,278 +4727,278 @@
     <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="26.862142857142857" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="8" width="22.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17" t="s">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="23">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="23">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="22"/>
+      <c r="E4" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="24"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="21">
+      <c r="E5" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="23">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="21">
+      <c r="E6" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="23">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="22"/>
+      <c r="E7" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="24"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="22"/>
+      <c r="E8" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="24"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="21">
+      <c r="E9" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="23">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="21">
+      <c r="E10" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="23">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="23">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="23">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="22"/>
+      <c r="E13" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="24"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="E14" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="23">
+      <c r="E14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="25">
         <v>0</v>
       </c>
     </row>
@@ -4988,7 +5019,7 @@
     <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -5089,11 +5120,11 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="52.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -5194,12 +5225,12 @@
   <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="27.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="14.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="28.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="25.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="15" width="27.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="14.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="28.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="25.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
